--- a/data/input/log_decisions/log_decisions.xlsx
+++ b/data/input/log_decisions/log_decisions.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2ad4b7826eb0755/ECW/repositories/AnnualResultsReport/data/input/log_decisions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_F25DC773A252ABDACC10480E619B7F8A5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0DB694-C8EA-4FA7-847E-C9D5D08219EC}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC10480E619B7F8A5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F893791-83A5-4CA7-94D6-CCBD36553B59}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4830" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1152" yWindow="3516" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cr" sheetId="1" r:id="rId1"/>
     <sheet name="pr" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
